--- a/Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
+++ b/Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,11 @@
       <b val="1"/>
       <color rgb="000B1F3A"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005A6373"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -130,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +168,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -692,6 +698,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
